--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Development Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Structure" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Utah Property Tax Reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Development Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Debt Structure" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Utah Property Tax Reference" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3554,27 +3554,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E68"/>
+  <dimension ref="B1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Debt Structure (pricing day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Leave blank for preliminary analysis (uses the single flat rate / par). On pricing day enter per-maturity Coupon &amp; Yield; for a term bond, put its final maturity year in the Term column on each sinking row.</t>
+          <t>Debt Structure — Serialize / Term (pricing day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Leave blank for the flat-rate preliminary sizing. Otherwise, per maturity, enter: Par Amount (optional — blank lets the model size the amortization), Coupon, Yield, and Type = Serial or Term. Fill one row per SERIAL maturity. For a TERM bond, fill the row of its FINAL maturity and mark it Term; everything up to that maturity amortizes into it at that coupon/yield. A single Term row (e.g. 2056 · 6.00% · 6.36%) makes the WHOLE structure one amortizing term bond priced to that maturity. Prices run to worst call.</t>
         </is>
       </c>
     </row>
@@ -3593,17 +3594,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Par Amount</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>Coupon</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Term Final Maturity</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Type (Serial/Term)</t>
         </is>
       </c>
     </row>
@@ -3611,241 +3617,271 @@
       <c r="B6" s="15" t="n">
         <v>2025</v>
       </c>
-      <c r="C6" s="19" t="n"/>
+      <c r="C6" s="16" t="n"/>
       <c r="D6" s="19" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="15" t="n">
         <v>2026</v>
       </c>
-      <c r="C7" s="19" t="n"/>
+      <c r="C7" s="16" t="n"/>
       <c r="D7" s="19" t="n"/>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="15" t="n">
         <v>2027</v>
       </c>
-      <c r="C8" s="19" t="n"/>
+      <c r="C8" s="16" t="n"/>
       <c r="D8" s="19" t="n"/>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="15" t="n">
         <v>2028</v>
       </c>
-      <c r="C9" s="19" t="n"/>
+      <c r="C9" s="16" t="n"/>
       <c r="D9" s="19" t="n"/>
-      <c r="E9" s="15" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="15" t="n">
         <v>2029</v>
       </c>
-      <c r="C10" s="19" t="n"/>
+      <c r="C10" s="16" t="n"/>
       <c r="D10" s="19" t="n"/>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C11" s="19" t="n"/>
+      <c r="C11" s="16" t="n"/>
       <c r="D11" s="19" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="C12" s="19" t="n"/>
+      <c r="C12" s="16" t="n"/>
       <c r="D12" s="19" t="n"/>
-      <c r="E12" s="15" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="C13" s="19" t="n"/>
+      <c r="C13" s="16" t="n"/>
       <c r="D13" s="19" t="n"/>
-      <c r="E13" s="15" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="C14" s="19" t="n"/>
+      <c r="C14" s="16" t="n"/>
       <c r="D14" s="19" t="n"/>
-      <c r="E14" s="15" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="15" t="n">
         <v>2034</v>
       </c>
-      <c r="C15" s="19" t="n"/>
+      <c r="C15" s="16" t="n"/>
       <c r="D15" s="19" t="n"/>
-      <c r="E15" s="15" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="C16" s="19" t="n"/>
+      <c r="C16" s="16" t="n"/>
       <c r="D16" s="19" t="n"/>
-      <c r="E16" s="15" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="15" t="n">
         <v>2036</v>
       </c>
-      <c r="C17" s="19" t="n"/>
+      <c r="C17" s="16" t="n"/>
       <c r="D17" s="19" t="n"/>
-      <c r="E17" s="15" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="15" t="n">
         <v>2037</v>
       </c>
-      <c r="C18" s="19" t="n"/>
+      <c r="C18" s="16" t="n"/>
       <c r="D18" s="19" t="n"/>
-      <c r="E18" s="15" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="15" t="n">
         <v>2038</v>
       </c>
-      <c r="C19" s="19" t="n"/>
+      <c r="C19" s="16" t="n"/>
       <c r="D19" s="19" t="n"/>
-      <c r="E19" s="15" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="15" t="n">
         <v>2039</v>
       </c>
-      <c r="C20" s="19" t="n"/>
+      <c r="C20" s="16" t="n"/>
       <c r="D20" s="19" t="n"/>
-      <c r="E20" s="15" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C21" s="19" t="n"/>
+      <c r="C21" s="16" t="n"/>
       <c r="D21" s="19" t="n"/>
-      <c r="E21" s="15" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="15" t="n">
         <v>2041</v>
       </c>
-      <c r="C22" s="19" t="n"/>
+      <c r="C22" s="16" t="n"/>
       <c r="D22" s="19" t="n"/>
-      <c r="E22" s="15" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="15" t="n">
         <v>2042</v>
       </c>
-      <c r="C23" s="19" t="n"/>
+      <c r="C23" s="16" t="n"/>
       <c r="D23" s="19" t="n"/>
-      <c r="E23" s="15" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="15" t="n">
         <v>2043</v>
       </c>
-      <c r="C24" s="19" t="n"/>
+      <c r="C24" s="16" t="n"/>
       <c r="D24" s="19" t="n"/>
-      <c r="E24" s="15" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n">
         <v>2044</v>
       </c>
-      <c r="C25" s="19" t="n"/>
+      <c r="C25" s="16" t="n"/>
       <c r="D25" s="19" t="n"/>
-      <c r="E25" s="15" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="15" t="n">
         <v>2045</v>
       </c>
-      <c r="C26" s="19" t="n"/>
+      <c r="C26" s="16" t="n"/>
       <c r="D26" s="19" t="n"/>
-      <c r="E26" s="15" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="15" t="n">
         <v>2046</v>
       </c>
-      <c r="C27" s="19" t="n"/>
+      <c r="C27" s="16" t="n"/>
       <c r="D27" s="19" t="n"/>
-      <c r="E27" s="15" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="15" t="n">
         <v>2047</v>
       </c>
-      <c r="C28" s="19" t="n"/>
+      <c r="C28" s="16" t="n"/>
       <c r="D28" s="19" t="n"/>
-      <c r="E28" s="15" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="15" t="n">
         <v>2048</v>
       </c>
-      <c r="C29" s="19" t="n"/>
+      <c r="C29" s="16" t="n"/>
       <c r="D29" s="19" t="n"/>
-      <c r="E29" s="15" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="15" t="n">
         <v>2049</v>
       </c>
-      <c r="C30" s="19" t="n"/>
+      <c r="C30" s="16" t="n"/>
       <c r="D30" s="19" t="n"/>
-      <c r="E30" s="15" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" s="19" t="n"/>
+      <c r="C31" s="16" t="n"/>
       <c r="D31" s="19" t="n"/>
-      <c r="E31" s="15" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="15" t="n">
         <v>2051</v>
       </c>
-      <c r="C32" s="19" t="n"/>
+      <c r="C32" s="16" t="n"/>
       <c r="D32" s="19" t="n"/>
-      <c r="E32" s="15" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="15" t="n">
         <v>2052</v>
       </c>
-      <c r="C33" s="19" t="n"/>
+      <c r="C33" s="16" t="n"/>
       <c r="D33" s="19" t="n"/>
-      <c r="E33" s="15" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="15" t="n">
         <v>2053</v>
       </c>
-      <c r="C34" s="19" t="n"/>
+      <c r="C34" s="16" t="n"/>
       <c r="D34" s="19" t="n"/>
-      <c r="E34" s="15" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="15" t="n">
         <v>2054</v>
       </c>
-      <c r="C35" s="19" t="n"/>
+      <c r="C35" s="16" t="n"/>
       <c r="D35" s="19" t="n"/>
-      <c r="E35" s="15" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
@@ -3862,17 +3898,22 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
+          <t>Par Amount</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
           <t>Coupon</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Term Final Maturity</t>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Type (Serial/Term)</t>
         </is>
       </c>
     </row>
@@ -3880,249 +3921,284 @@
       <c r="B39" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="C39" s="19" t="n"/>
+      <c r="C39" s="16" t="n"/>
       <c r="D39" s="19" t="n"/>
-      <c r="E39" s="15" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="C40" s="19" t="n"/>
+      <c r="C40" s="16" t="n"/>
       <c r="D40" s="19" t="n"/>
-      <c r="E40" s="15" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="C41" s="19" t="n"/>
+      <c r="C41" s="16" t="n"/>
       <c r="D41" s="19" t="n"/>
-      <c r="E41" s="15" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="C42" s="19" t="n"/>
+      <c r="C42" s="16" t="n"/>
       <c r="D42" s="19" t="n"/>
-      <c r="E42" s="15" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="15" t="n">
         <v>2034</v>
       </c>
-      <c r="C43" s="19" t="n"/>
+      <c r="C43" s="16" t="n"/>
       <c r="D43" s="19" t="n"/>
-      <c r="E43" s="15" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="15" t="n">
         <v>2035</v>
       </c>
-      <c r="C44" s="19" t="n"/>
+      <c r="C44" s="16" t="n"/>
       <c r="D44" s="19" t="n"/>
-      <c r="E44" s="15" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="15" t="n">
         <v>2036</v>
       </c>
-      <c r="C45" s="19" t="n"/>
+      <c r="C45" s="16" t="n"/>
       <c r="D45" s="19" t="n"/>
-      <c r="E45" s="15" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="15" t="n">
         <v>2037</v>
       </c>
-      <c r="C46" s="19" t="n"/>
+      <c r="C46" s="16" t="n"/>
       <c r="D46" s="19" t="n"/>
-      <c r="E46" s="15" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="15" t="n">
         <v>2038</v>
       </c>
-      <c r="C47" s="19" t="n"/>
+      <c r="C47" s="16" t="n"/>
       <c r="D47" s="19" t="n"/>
-      <c r="E47" s="15" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="15" t="n">
         <v>2039</v>
       </c>
-      <c r="C48" s="19" t="n"/>
+      <c r="C48" s="16" t="n"/>
       <c r="D48" s="19" t="n"/>
-      <c r="E48" s="15" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="15" t="n">
         <v>2040</v>
       </c>
-      <c r="C49" s="19" t="n"/>
+      <c r="C49" s="16" t="n"/>
       <c r="D49" s="19" t="n"/>
-      <c r="E49" s="15" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="15" t="n">
         <v>2041</v>
       </c>
-      <c r="C50" s="19" t="n"/>
+      <c r="C50" s="16" t="n"/>
       <c r="D50" s="19" t="n"/>
-      <c r="E50" s="15" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="15" t="n">
         <v>2042</v>
       </c>
-      <c r="C51" s="19" t="n"/>
+      <c r="C51" s="16" t="n"/>
       <c r="D51" s="19" t="n"/>
-      <c r="E51" s="15" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="15" t="n">
         <v>2043</v>
       </c>
-      <c r="C52" s="19" t="n"/>
+      <c r="C52" s="16" t="n"/>
       <c r="D52" s="19" t="n"/>
-      <c r="E52" s="15" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="15" t="n">
         <v>2044</v>
       </c>
-      <c r="C53" s="19" t="n"/>
+      <c r="C53" s="16" t="n"/>
       <c r="D53" s="19" t="n"/>
-      <c r="E53" s="15" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="15" t="n">
         <v>2045</v>
       </c>
-      <c r="C54" s="19" t="n"/>
+      <c r="C54" s="16" t="n"/>
       <c r="D54" s="19" t="n"/>
-      <c r="E54" s="15" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="15" t="n">
         <v>2046</v>
       </c>
-      <c r="C55" s="19" t="n"/>
+      <c r="C55" s="16" t="n"/>
       <c r="D55" s="19" t="n"/>
-      <c r="E55" s="15" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="15" t="n">
         <v>2047</v>
       </c>
-      <c r="C56" s="19" t="n"/>
+      <c r="C56" s="16" t="n"/>
       <c r="D56" s="19" t="n"/>
-      <c r="E56" s="15" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="15" t="n">
         <v>2048</v>
       </c>
-      <c r="C57" s="19" t="n"/>
+      <c r="C57" s="16" t="n"/>
       <c r="D57" s="19" t="n"/>
-      <c r="E57" s="15" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="15" t="n">
         <v>2049</v>
       </c>
-      <c r="C58" s="19" t="n"/>
+      <c r="C58" s="16" t="n"/>
       <c r="D58" s="19" t="n"/>
-      <c r="E58" s="15" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="15" t="n">
         <v>2050</v>
       </c>
-      <c r="C59" s="19" t="n"/>
+      <c r="C59" s="16" t="n"/>
       <c r="D59" s="19" t="n"/>
-      <c r="E59" s="15" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="15" t="n">
         <v>2051</v>
       </c>
-      <c r="C60" s="19" t="n"/>
+      <c r="C60" s="16" t="n"/>
       <c r="D60" s="19" t="n"/>
-      <c r="E60" s="15" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="15" t="n">
         <v>2052</v>
       </c>
-      <c r="C61" s="19" t="n"/>
+      <c r="C61" s="16" t="n"/>
       <c r="D61" s="19" t="n"/>
-      <c r="E61" s="15" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="15" t="n">
         <v>2053</v>
       </c>
-      <c r="C62" s="19" t="n"/>
+      <c r="C62" s="16" t="n"/>
       <c r="D62" s="19" t="n"/>
-      <c r="E62" s="15" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="15" t="n">
         <v>2054</v>
       </c>
-      <c r="C63" s="19" t="n"/>
+      <c r="C63" s="16" t="n"/>
       <c r="D63" s="19" t="n"/>
-      <c r="E63" s="15" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="15" t="n">
         <v>2055</v>
       </c>
-      <c r="C64" s="19" t="n"/>
+      <c r="C64" s="16" t="n"/>
       <c r="D64" s="19" t="n"/>
-      <c r="E64" s="15" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="15" t="n">
         <v>2056</v>
       </c>
-      <c r="C65" s="19" t="n"/>
+      <c r="C65" s="16" t="n"/>
       <c r="D65" s="19" t="n"/>
-      <c r="E65" s="15" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="15" t="n">
         <v>2057</v>
       </c>
-      <c r="C66" s="19" t="n"/>
+      <c r="C66" s="16" t="n"/>
       <c r="D66" s="19" t="n"/>
-      <c r="E66" s="15" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="15" t="n">
         <v>2058</v>
       </c>
-      <c r="C67" s="19" t="n"/>
+      <c r="C67" s="16" t="n"/>
       <c r="D67" s="19" t="n"/>
-      <c r="E67" s="15" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="15" t="n">
         <v>2059</v>
       </c>
-      <c r="C68" s="19" t="n"/>
+      <c r="C68" s="16" t="n"/>
       <c r="D68" s="19" t="n"/>
-      <c r="E68" s="15" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Serial,Term"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy.m.d"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -19,11 +19,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
     <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -115,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +171,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3554,7 +3558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F68"/>
+  <dimension ref="B1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3563,6 +3567,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3575,7 +3580,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Leave blank for the flat-rate preliminary sizing. Otherwise, per maturity, enter: Par Amount (optional — blank lets the model size the amortization), Coupon, Yield, and Type = Serial or Term. Fill one row per SERIAL maturity. For a TERM bond, fill the row of its FINAL maturity and mark it Term; everything up to that maturity amortizes into it at that coupon/yield. A single Term row (e.g. 2056 · 6.00% · 6.36%) makes the WHOLE structure one amortizing term bond priced to that maturity. Prices run to worst call.</t>
+          <t>Leave blank for the flat-rate preliminary sizing. Otherwise, per maturity, enter: Par Amount (optional — blank lets the model size the amortization), Coupon, Yield, and Type = Serial or Term. Fill one row per SERIAL maturity. For a TERM bond, fill the row of its FINAL maturity and mark it Term; everything up to that maturity amortizes into it at that coupon/yield. A single Term row (e.g. 2056 · 6.00% · 6.36%) makes the WHOLE structure one amortizing term bond priced to that maturity. Prices run to worst call. Price is optional: leave it blank and the model computes it from the coupon and yield; enter the underwriter's price (e.g. 95.148) and that price governs the OID outright.</t>
         </is>
       </c>
     </row>
@@ -3610,6 +3615,11 @@
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Type (Serial/Term)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Price (optional)</t>
         </is>
       </c>
     </row>
@@ -3621,6 +3631,7 @@
       <c r="D6" s="19" t="n"/>
       <c r="E6" s="19" t="n"/>
       <c r="F6" s="15" t="n"/>
+      <c r="G6" s="20" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="15" t="n">
@@ -3630,6 +3641,7 @@
       <c r="D7" s="19" t="n"/>
       <c r="E7" s="19" t="n"/>
       <c r="F7" s="15" t="n"/>
+      <c r="G7" s="20" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="15" t="n">
@@ -3639,6 +3651,7 @@
       <c r="D8" s="19" t="n"/>
       <c r="E8" s="19" t="n"/>
       <c r="F8" s="15" t="n"/>
+      <c r="G8" s="20" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="15" t="n">
@@ -3648,6 +3661,7 @@
       <c r="D9" s="19" t="n"/>
       <c r="E9" s="19" t="n"/>
       <c r="F9" s="15" t="n"/>
+      <c r="G9" s="20" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="15" t="n">
@@ -3657,6 +3671,7 @@
       <c r="D10" s="19" t="n"/>
       <c r="E10" s="19" t="n"/>
       <c r="F10" s="15" t="n"/>
+      <c r="G10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="15" t="n">
@@ -3666,6 +3681,7 @@
       <c r="D11" s="19" t="n"/>
       <c r="E11" s="19" t="n"/>
       <c r="F11" s="15" t="n"/>
+      <c r="G11" s="20" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="15" t="n">
@@ -3675,6 +3691,7 @@
       <c r="D12" s="19" t="n"/>
       <c r="E12" s="19" t="n"/>
       <c r="F12" s="15" t="n"/>
+      <c r="G12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="15" t="n">
@@ -3684,6 +3701,7 @@
       <c r="D13" s="19" t="n"/>
       <c r="E13" s="19" t="n"/>
       <c r="F13" s="15" t="n"/>
+      <c r="G13" s="20" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="15" t="n">
@@ -3693,6 +3711,7 @@
       <c r="D14" s="19" t="n"/>
       <c r="E14" s="19" t="n"/>
       <c r="F14" s="15" t="n"/>
+      <c r="G14" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="15" t="n">
@@ -3702,6 +3721,7 @@
       <c r="D15" s="19" t="n"/>
       <c r="E15" s="19" t="n"/>
       <c r="F15" s="15" t="n"/>
+      <c r="G15" s="20" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="15" t="n">
@@ -3711,6 +3731,7 @@
       <c r="D16" s="19" t="n"/>
       <c r="E16" s="19" t="n"/>
       <c r="F16" s="15" t="n"/>
+      <c r="G16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="15" t="n">
@@ -3720,6 +3741,7 @@
       <c r="D17" s="19" t="n"/>
       <c r="E17" s="19" t="n"/>
       <c r="F17" s="15" t="n"/>
+      <c r="G17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="15" t="n">
@@ -3729,6 +3751,7 @@
       <c r="D18" s="19" t="n"/>
       <c r="E18" s="19" t="n"/>
       <c r="F18" s="15" t="n"/>
+      <c r="G18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="15" t="n">
@@ -3738,6 +3761,7 @@
       <c r="D19" s="19" t="n"/>
       <c r="E19" s="19" t="n"/>
       <c r="F19" s="15" t="n"/>
+      <c r="G19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="15" t="n">
@@ -3747,6 +3771,7 @@
       <c r="D20" s="19" t="n"/>
       <c r="E20" s="19" t="n"/>
       <c r="F20" s="15" t="n"/>
+      <c r="G20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="15" t="n">
@@ -3756,6 +3781,7 @@
       <c r="D21" s="19" t="n"/>
       <c r="E21" s="19" t="n"/>
       <c r="F21" s="15" t="n"/>
+      <c r="G21" s="20" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="15" t="n">
@@ -3765,6 +3791,7 @@
       <c r="D22" s="19" t="n"/>
       <c r="E22" s="19" t="n"/>
       <c r="F22" s="15" t="n"/>
+      <c r="G22" s="20" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="15" t="n">
@@ -3774,6 +3801,7 @@
       <c r="D23" s="19" t="n"/>
       <c r="E23" s="19" t="n"/>
       <c r="F23" s="15" t="n"/>
+      <c r="G23" s="20" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="15" t="n">
@@ -3783,6 +3811,7 @@
       <c r="D24" s="19" t="n"/>
       <c r="E24" s="19" t="n"/>
       <c r="F24" s="15" t="n"/>
+      <c r="G24" s="20" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="15" t="n">
@@ -3792,6 +3821,7 @@
       <c r="D25" s="19" t="n"/>
       <c r="E25" s="19" t="n"/>
       <c r="F25" s="15" t="n"/>
+      <c r="G25" s="20" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="15" t="n">
@@ -3801,6 +3831,7 @@
       <c r="D26" s="19" t="n"/>
       <c r="E26" s="19" t="n"/>
       <c r="F26" s="15" t="n"/>
+      <c r="G26" s="20" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="15" t="n">
@@ -3810,6 +3841,7 @@
       <c r="D27" s="19" t="n"/>
       <c r="E27" s="19" t="n"/>
       <c r="F27" s="15" t="n"/>
+      <c r="G27" s="20" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="15" t="n">
@@ -3819,6 +3851,7 @@
       <c r="D28" s="19" t="n"/>
       <c r="E28" s="19" t="n"/>
       <c r="F28" s="15" t="n"/>
+      <c r="G28" s="20" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="15" t="n">
@@ -3828,6 +3861,7 @@
       <c r="D29" s="19" t="n"/>
       <c r="E29" s="19" t="n"/>
       <c r="F29" s="15" t="n"/>
+      <c r="G29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="15" t="n">
@@ -3837,6 +3871,7 @@
       <c r="D30" s="19" t="n"/>
       <c r="E30" s="19" t="n"/>
       <c r="F30" s="15" t="n"/>
+      <c r="G30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="15" t="n">
@@ -3846,6 +3881,7 @@
       <c r="D31" s="19" t="n"/>
       <c r="E31" s="19" t="n"/>
       <c r="F31" s="15" t="n"/>
+      <c r="G31" s="20" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="15" t="n">
@@ -3855,6 +3891,7 @@
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
       <c r="F32" s="15" t="n"/>
+      <c r="G32" s="20" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="15" t="n">
@@ -3864,6 +3901,7 @@
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="15" t="n"/>
+      <c r="G33" s="20" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="15" t="n">
@@ -3873,6 +3911,7 @@
       <c r="D34" s="19" t="n"/>
       <c r="E34" s="19" t="n"/>
       <c r="F34" s="15" t="n"/>
+      <c r="G34" s="20" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="15" t="n">
@@ -3882,6 +3921,7 @@
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="15" t="n"/>
+      <c r="G35" s="20" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
@@ -3914,6 +3954,11 @@
       <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Type (Serial/Term)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Price (optional)</t>
         </is>
       </c>
     </row>
@@ -3925,6 +3970,7 @@
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="19" t="n"/>
       <c r="F39" s="15" t="n"/>
+      <c r="G39" s="20" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="15" t="n">
@@ -3934,6 +3980,7 @@
       <c r="D40" s="19" t="n"/>
       <c r="E40" s="19" t="n"/>
       <c r="F40" s="15" t="n"/>
+      <c r="G40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="15" t="n">
@@ -3943,6 +3990,7 @@
       <c r="D41" s="19" t="n"/>
       <c r="E41" s="19" t="n"/>
       <c r="F41" s="15" t="n"/>
+      <c r="G41" s="20" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="15" t="n">
@@ -3952,6 +4000,7 @@
       <c r="D42" s="19" t="n"/>
       <c r="E42" s="19" t="n"/>
       <c r="F42" s="15" t="n"/>
+      <c r="G42" s="20" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="15" t="n">
@@ -3961,6 +4010,7 @@
       <c r="D43" s="19" t="n"/>
       <c r="E43" s="19" t="n"/>
       <c r="F43" s="15" t="n"/>
+      <c r="G43" s="20" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="15" t="n">
@@ -3970,6 +4020,7 @@
       <c r="D44" s="19" t="n"/>
       <c r="E44" s="19" t="n"/>
       <c r="F44" s="15" t="n"/>
+      <c r="G44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="15" t="n">
@@ -3979,6 +4030,7 @@
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="15" t="n"/>
+      <c r="G45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="15" t="n">
@@ -3988,6 +4040,7 @@
       <c r="D46" s="19" t="n"/>
       <c r="E46" s="19" t="n"/>
       <c r="F46" s="15" t="n"/>
+      <c r="G46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="15" t="n">
@@ -3997,6 +4050,7 @@
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="n"/>
       <c r="F47" s="15" t="n"/>
+      <c r="G47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="15" t="n">
@@ -4006,6 +4060,7 @@
       <c r="D48" s="19" t="n"/>
       <c r="E48" s="19" t="n"/>
       <c r="F48" s="15" t="n"/>
+      <c r="G48" s="20" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="15" t="n">
@@ -4015,6 +4070,7 @@
       <c r="D49" s="19" t="n"/>
       <c r="E49" s="19" t="n"/>
       <c r="F49" s="15" t="n"/>
+      <c r="G49" s="20" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="15" t="n">
@@ -4024,6 +4080,7 @@
       <c r="D50" s="19" t="n"/>
       <c r="E50" s="19" t="n"/>
       <c r="F50" s="15" t="n"/>
+      <c r="G50" s="20" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="15" t="n">
@@ -4033,6 +4090,7 @@
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="15" t="n"/>
+      <c r="G51" s="20" t="n"/>
     </row>
     <row r="52">
       <c r="B52" s="15" t="n">
@@ -4042,6 +4100,7 @@
       <c r="D52" s="19" t="n"/>
       <c r="E52" s="19" t="n"/>
       <c r="F52" s="15" t="n"/>
+      <c r="G52" s="20" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="15" t="n">
@@ -4051,6 +4110,7 @@
       <c r="D53" s="19" t="n"/>
       <c r="E53" s="19" t="n"/>
       <c r="F53" s="15" t="n"/>
+      <c r="G53" s="20" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="15" t="n">
@@ -4060,6 +4120,7 @@
       <c r="D54" s="19" t="n"/>
       <c r="E54" s="19" t="n"/>
       <c r="F54" s="15" t="n"/>
+      <c r="G54" s="20" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="15" t="n">
@@ -4069,6 +4130,7 @@
       <c r="D55" s="19" t="n"/>
       <c r="E55" s="19" t="n"/>
       <c r="F55" s="15" t="n"/>
+      <c r="G55" s="20" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="15" t="n">
@@ -4078,6 +4140,7 @@
       <c r="D56" s="19" t="n"/>
       <c r="E56" s="19" t="n"/>
       <c r="F56" s="15" t="n"/>
+      <c r="G56" s="20" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="15" t="n">
@@ -4087,6 +4150,7 @@
       <c r="D57" s="19" t="n"/>
       <c r="E57" s="19" t="n"/>
       <c r="F57" s="15" t="n"/>
+      <c r="G57" s="20" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="15" t="n">
@@ -4096,6 +4160,7 @@
       <c r="D58" s="19" t="n"/>
       <c r="E58" s="19" t="n"/>
       <c r="F58" s="15" t="n"/>
+      <c r="G58" s="20" t="n"/>
     </row>
     <row r="59">
       <c r="B59" s="15" t="n">
@@ -4105,6 +4170,7 @@
       <c r="D59" s="19" t="n"/>
       <c r="E59" s="19" t="n"/>
       <c r="F59" s="15" t="n"/>
+      <c r="G59" s="20" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="15" t="n">
@@ -4114,6 +4180,7 @@
       <c r="D60" s="19" t="n"/>
       <c r="E60" s="19" t="n"/>
       <c r="F60" s="15" t="n"/>
+      <c r="G60" s="20" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="15" t="n">
@@ -4123,6 +4190,7 @@
       <c r="D61" s="19" t="n"/>
       <c r="E61" s="19" t="n"/>
       <c r="F61" s="15" t="n"/>
+      <c r="G61" s="20" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="15" t="n">
@@ -4132,6 +4200,7 @@
       <c r="D62" s="19" t="n"/>
       <c r="E62" s="19" t="n"/>
       <c r="F62" s="15" t="n"/>
+      <c r="G62" s="20" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="15" t="n">
@@ -4141,6 +4210,7 @@
       <c r="D63" s="19" t="n"/>
       <c r="E63" s="19" t="n"/>
       <c r="F63" s="15" t="n"/>
+      <c r="G63" s="20" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="15" t="n">
@@ -4150,6 +4220,7 @@
       <c r="D64" s="19" t="n"/>
       <c r="E64" s="19" t="n"/>
       <c r="F64" s="15" t="n"/>
+      <c r="G64" s="20" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="15" t="n">
@@ -4159,6 +4230,7 @@
       <c r="D65" s="19" t="n"/>
       <c r="E65" s="19" t="n"/>
       <c r="F65" s="15" t="n"/>
+      <c r="G65" s="20" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="15" t="n">
@@ -4168,6 +4240,7 @@
       <c r="D66" s="19" t="n"/>
       <c r="E66" s="19" t="n"/>
       <c r="F66" s="15" t="n"/>
+      <c r="G66" s="20" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="15" t="n">
@@ -4177,6 +4250,7 @@
       <c r="D67" s="19" t="n"/>
       <c r="E67" s="19" t="n"/>
       <c r="F67" s="15" t="n"/>
+      <c r="G67" s="20" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="15" t="n">
@@ -4186,13 +4260,14 @@
       <c r="D68" s="19" t="n"/>
       <c r="E68" s="19" t="n"/>
       <c r="F68" s="15" t="n"/>
+      <c r="G68" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4250,7 +4325,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>1982–1984</t>
         </is>
@@ -4265,7 +4340,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>1985–1994</t>
         </is>
@@ -4280,7 +4355,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>1995 +</t>
         </is>
@@ -4326,7 +4401,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>1995 +</t>
         </is>
@@ -4367,7 +4442,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>January 1</t>
         </is>
@@ -4379,7 +4454,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>May 1</t>
         </is>
@@ -4391,7 +4466,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>May 22</t>
         </is>
@@ -4403,7 +4478,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>June 8</t>
         </is>
@@ -4415,7 +4490,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>June 22</t>
         </is>
@@ -4427,7 +4502,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>July 22</t>
         </is>
@@ -4439,7 +4514,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>November 1</t>
         </is>
@@ -4451,7 +4526,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>November 30</t>
         </is>
@@ -4463,7 +4538,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>December 31</t>
         </is>
@@ -4475,7 +4550,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>January 1 (next)</t>
         </is>
@@ -4487,7 +4562,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>

--- a/ut_pid_model_inputs - Viridian Farm.xlsx
+++ b/ut_pid_model_inputs - Viridian Farm.xlsx
@@ -547,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K105"/>
+  <dimension ref="B1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1975,62 +1975,51 @@
     <row r="82">
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Mill Levies</t>
+          <t>Bond Structure</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy — Governing Document Cap</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="n">
-        <v>5</v>
+          <t>Interest Payment Frequency</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Semiannual</t>
+        </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_GOVERNING_DOC</t>
+          <t>INTEREST_FREQUENCY</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>mills</t>
+          <t>Semiannual (2 coupons a year) or Annual (1); drives the schedule and the price</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>Mill Levy — Indenture Cap</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>MILL_LEVY_INDENTURE</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>mills; blank ⇒ no indenture cap</t>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Mill Levies</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy Target - Debt Service</t>
+          <t>Mill Levy — Governing Document Cap</t>
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_DS_TARGET</t>
+          <t>MILL_LEVY_GOVERNING_DOC</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
@@ -2042,7 +2031,7 @@
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy - Commercial</t>
+          <t>Mill Levy — Indenture Cap</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
@@ -2050,27 +2039,27 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_COMM</t>
+          <t>MILL_LEVY_INDENTURE</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>mills</t>
+          <t>mills; blank ⇒ no indenture cap</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Mill Levy Target - Operations</t>
+          <t>Mill Levy Target - Debt Service</t>
         </is>
       </c>
       <c r="C87" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>MILL_LEVY_OPS_TARGET</t>
+          <t>MILL_LEVY_DS_TARGET</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -2080,329 +2069,373 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Lot / Home Ratios</t>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Mill Levy - Commercial</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>MILL_LEVY_COMM</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>mills</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Builder Lot Inventory Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C89" s="12" t="n">
-        <v>0.55</v>
+          <t>Mill Levy Target - Operations</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>LOT_INVENTORY_TAXABLE_RATIO</t>
+          <t>MILL_LEVY_OPS_TARGET</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>55% under Utah Admin. Code R884-24P-52; 100% to tax at full market</t>
+          <t>mills</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Lot / Home Valuation</t>
+          <t>Lot / Home Ratios</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
+          <t>Builder Lot Inventory Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>LOT_INVENTORY_TAXABLE_RATIO</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>55% under Utah Admin. Code R884-24P-52; 100% to tax at full market</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Lot / Home Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="6" t="inlineStr">
+        <is>
           <t>Platted Lot Value (% of ASP)</t>
         </is>
       </c>
-      <c r="C91" s="12" t="n">
+      <c r="C93" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>PLATTED_LOT_VALUE</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>lot value = ASP × this (default 10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Platted Commercial Lot Value</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>PLATTED_COMM_LOT_VALUE</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Centrally Assessed / Commercial</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Property (market value)</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="n">
-        <v>0</v>
+          <t>Platted Commercial Lot Value</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>0.1</v>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_VALUE</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>$ market — § 59-2-201</t>
-        </is>
-      </c>
+          <t>PLATTED_COMM_LOT_VALUE</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Centrally Assessed Equipment (market value)</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="8" t="inlineStr">
-        <is>
-          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
-        <is>
-          <t>$ market</t>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Centrally Assessed / Commercial</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Centrally Assessed Taxable Ratio</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>0.875</v>
+          <t>Centrally Assessed Property (market value)</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED_RATIO</t>
+          <t>CENTRALLY_ASSESSED_VALUE</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>market value × ratio</t>
+          <t>$ market — § 59-2-201</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Include Centrally Assessed in Taxed Value</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Centrally Assessed Equipment (market value)</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>CENTRALLY_ASSESSED</t>
+          <t>CENTRALLY_ASSESSED_EQUIPMENT</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>Yes/No</t>
+          <t>$ market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Commercial Taxable Ratio</t>
+          <t>Centrally Assessed Taxable Ratio</t>
         </is>
       </c>
       <c r="C98" s="12" t="n">
-        <v>0.29</v>
+        <v>0.875</v>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr"/>
+          <t>CENTRALLY_ASSESSED_RATIO</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>market value × ratio</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Commercial AV Lag (years)</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="n">
-        <v>2</v>
+          <t>Include Centrally Assessed in Taxed Value</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>COMM_ASSESSMENT_LAG_YEARS</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr"/>
+          <t>CENTRALLY_ASSESSED</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Yes/No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Include Commercial in Taxed AV</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Commercial Taxable Ratio</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>0.29</v>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>COMM_NEW_VALUE_ADD</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
-        <is>
-          <t>Yes/No</t>
-        </is>
-      </c>
+          <t>COMMERCIAL_ASSESSMENT_RATIO</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>District Costs</t>
-        </is>
-      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Commercial AV Lag (years)</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>COMM_ASSESSMENT_LAG_YEARS</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Starting O&amp;M Expense</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="n">
-        <v>53060</v>
+          <t>Include Commercial in Taxed AV</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>OM_EXPENSE</t>
+          <t>COMM_NEW_VALUE_ADD</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>$ per year of district operations &amp; administration, netted from the revenue available to both liens</t>
+          <t>Yes/No</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>O&amp;M Expense Growth Rate</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t>OM_GROWTH_RATE</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>annual inflation on the O&amp;M base</t>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>District Costs</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>O&amp;M Expense Taxable Value Limit</t>
+          <t>Starting O&amp;M Expense</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>0</v>
+        <v>53060</v>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>OM_EXPENSE_AV_LIMIT</t>
+          <t>OM_EXPENSE</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
+          <t>$ per year of district operations &amp; administration, netted from the revenue available to both liens</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
+          <t>O&amp;M Expense Growth Rate</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>OM_GROWTH_RATE</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>annual inflation on the O&amp;M base</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>O&amp;M Expense Taxable Value Limit</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>OM_EXPENSE_AV_LIMIT</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>$ — above this taxable value the charge stops; 0 ⇒ no limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
+        <is>
           <t>First Year District Costs Are Charged</t>
         </is>
       </c>
-      <c r="C105" s="7" t="n"/>
-      <c r="D105" s="8" t="inlineStr">
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>DISTRICT_COST_START_YEAR</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>blank ⇒ two years after closing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="B92:E92"/>
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B95:E95"/>
     <mergeCell ref="B75:E75"/>
     <mergeCell ref="B62:E62"/>
     <mergeCell ref="B72:E72"/>
     <mergeCell ref="B90:E90"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B93:E93"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B56:E56"/>
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="G5:K5"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B101:E101"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B88:E88"/>
     <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B103:E103"/>
     <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B84:E84"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="C19 C20 C21 C22 C23 C97 C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="C83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Semiannual,Annual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19 C20 C21 C22 C23 C99 C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="C61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
